--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N32_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.9951550664907</v>
+        <v>6.66171269830474</v>
       </c>
       <c r="D2" t="n">
-        <v>19.14418971907665</v>
+        <v>3.110930829349955</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
